--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>137076768</v>
       </c>
       <c r="B6" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>137076769</v>
       </c>
       <c r="B7" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19258-2026 artfynd.xlsx
+++ b/artfynd/A 19258-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137076764</v>
       </c>
       <c r="B2" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137076765</v>
       </c>
       <c r="B3" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137076763</v>
       </c>
       <c r="B4" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137076771</v>
       </c>
       <c r="B5" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>137076767</v>
       </c>
       <c r="B8" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
